--- a/Hoadon/HD2026/HDVao/8/3502469834_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HD2026/HDVao/8/3502469834_HDDienTuMayTinhTien.xlsx
@@ -722,37 +722,37 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C26MMQ</t>
+          <t>C26MTH</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>17236</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3502479416</t>
+          <t>077094004359</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THỰC PHẨM MINH QUÂN FOOD</t>
+          <t>HỘ KINH DOANH HẢI SẢN TƯ HÀ</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Số 516 đường Thống Nhất ,Phường Tam Thắng ,Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>10 Hoàng Hoa Thám, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -766,17 +766,13 @@
         </is>
       </c>
       <c r="K13" s="6"/>
-      <c r="L13" s="13" t="n">
-        <v>605000.0</v>
-      </c>
-      <c r="M13" s="13" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
       <c r="N13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>605000.0</v>
+        <v>190000.0</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -805,12 +801,12 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>17403</t>
+          <t>17236</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -840,23 +836,242 @@
       </c>
       <c r="K14" s="6"/>
       <c r="L14" s="13" t="n">
+        <v>605000.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O14" s="13" t="n">
+        <v>605000.0</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C26MMQ</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>17403</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>3502479416</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THỰC PHẨM MINH QUÂN FOOD</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Số 516 đường Thống Nhất ,Phường Tam Thắng ,Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K15" s="6"/>
+      <c r="L15" s="13" t="n">
         <v>555556.0</v>
       </c>
-      <c r="M14" s="13" t="n">
+      <c r="M15" s="13" t="n">
         <v>44444.0</v>
       </c>
-      <c r="N14" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O14" s="13" t="n">
+      <c r="N15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="13" t="n">
         <v>600000.0</v>
       </c>
-      <c r="P14" s="6" t="inlineStr">
+      <c r="P15" s="6" t="inlineStr">
         <is>
           <t>Hóa đơn mới</t>
         </is>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C26MMQ</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>17547</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>3502479416</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THỰC PHẨM MINH QUÂN FOOD</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Số 516 đường Thống Nhất ,Phường Tam Thắng ,Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K16" s="6"/>
+      <c r="L16" s="13" t="n">
+        <v>561000.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="13" t="n">
+        <v>561000.0</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>C26MTL</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>50686</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>3502549021</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THÀNH LẬP KHÁNH LINH</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>11-15-15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K17" s="6"/>
+      <c r="L17" s="13" t="n">
+        <v>4670740.0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>231260.0</v>
+      </c>
+      <c r="N17" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O17" s="13" t="n">
+        <v>4902000.0</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>
